--- a/education_forms/047_child_travel_consent_form--education_forms.xlsx
+++ b/education_forms/047_child_travel_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,8 +916,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_my_child_may_attend',_'value':_true}</t>
+          <t>yes_-_my_child_may_attend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - My child may attend', 'value': True}</t>
+          <t>Yes - My child may attend</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_my_child_will_not_attend',_'value':_false}</t>
+          <t>no_-_my_child_will_not_attend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No - My child will not attend', 'value': False}</t>
+          <t>No - My child will not attend</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'provided_school_bus',_'value':_'bus'}</t>
+          <t>provided_school_bus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Provided School Bus', 'value': 'bus'}</t>
+          <t>Provided School Bus</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'public_transit_or_rail',_'value':_'public'}</t>
+          <t>public_transit_or_rail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Public Transit or Rail', 'value': 'public'}</t>
+          <t>Public Transit or Rail</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'walking_to_local_site',_'value':_'walking'}</t>
+          <t>walking_to_local_site</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Walking to local site', 'value': 'walking'}</t>
+          <t>Walking to local site</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'i_authorize',_'value':_true}</t>
+          <t>i_authorize</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'I Authorize', 'value': True}</t>
+          <t>I Authorize</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_authorize',_'value':_false}</t>
+          <t>i_do_not_authorize</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I Do Not Authorize', 'value': False}</t>
+          <t>I Do Not Authorize</t>
         </is>
       </c>
     </row>
